--- a/backend/Rwanda/fuel-financial-inputs-{template}.xlsx
+++ b/backend/Rwanda/fuel-financial-inputs-{template}.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agarr\OneDrive\Escritorio\IIT\CC-WBT\backend\{templates}\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD95B9B-1AFB-41C2-858E-4F8E1A8D8AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{7CD95B9B-1AFB-41C2-858E-4F8E1A8D8AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3D77BA0-5D01-4B09-935B-6F2CD7D34744}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,15 +35,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="14">
   <si>
     <t>Inputs</t>
   </si>
   <si>
     <t>Units</t>
-  </si>
-  <si>
-    <t>Baseline</t>
   </si>
   <si>
     <t>Expected non-technical losses</t>
@@ -546,8 +543,8 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
+      <c r="C1" s="3">
+        <v>2020</v>
       </c>
       <c r="D1" s="3">
         <v>2021</v>
@@ -672,10 +669,10 @@
     </row>
     <row r="2" spans="1:43" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>4</v>
       </c>
       <c r="C2" s="6">
         <v>0</v>
@@ -803,10 +800,10 @@
     </row>
     <row r="3" spans="1:43" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>6</v>
       </c>
       <c r="C3" s="6">
         <v>0</v>
@@ -934,10 +931,10 @@
     </row>
     <row r="4" spans="1:43" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="6">
         <v>0</v>
@@ -1085,8 +1082,8 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
+      <c r="C1" s="3">
+        <v>2020</v>
       </c>
       <c r="D1" s="3">
         <v>2021</v>
@@ -1211,10 +1208,10 @@
     </row>
     <row r="2" spans="1:43" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>4</v>
       </c>
       <c r="C2" s="6">
         <v>0</v>
@@ -1342,10 +1339,10 @@
     </row>
     <row r="3" spans="1:43" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>6</v>
       </c>
       <c r="C3" s="6">
         <v>0</v>
@@ -1473,10 +1470,10 @@
     </row>
     <row r="4" spans="1:43" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="6">
         <v>0</v>
@@ -1624,8 +1621,8 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
+      <c r="C1" s="3">
+        <v>2020</v>
       </c>
       <c r="D1" s="3">
         <v>2021</v>
@@ -1750,10 +1747,10 @@
     </row>
     <row r="2" spans="1:43" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="6">
         <v>0</v>
@@ -1881,10 +1878,10 @@
     </row>
     <row r="3" spans="1:43" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="6">
         <v>0</v>
@@ -2012,10 +2009,10 @@
     </row>
     <row r="4" spans="1:43" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="6">
         <v>0</v>
@@ -2143,133 +2140,133 @@
     </row>
     <row r="5" spans="1:43" ht="16" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>13</v>
-      </c>
       <c r="C5" s="6">
         <v>0</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="X5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AB5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
